--- a/data/trans_camb/P2C_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R2-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,67; 20,66</t>
+          <t>11,03; 21,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 7,51</t>
+          <t>-1,83; 8,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,84; -13,48</t>
+          <t>-22,11; -13,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,4; 19,43</t>
+          <t>8,1; 19,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 3,67</t>
+          <t>-6,36; 3,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,1; -17,43</t>
+          <t>-26,78; -17,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,49; 19,07</t>
+          <t>11,27; 18,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 4,6</t>
+          <t>-3,04; 4,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-23,28; -16,53</t>
+          <t>-23,03; -16,84</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,62; 72,53</t>
+          <t>33,58; 76,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 26,18</t>
+          <t>-6,38; 29,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-65,68; -46,28</t>
+          <t>-66,12; -45,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,99; 54,47</t>
+          <t>20,26; 55,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 10,12</t>
+          <t>-15,37; 10,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,42; -49,34</t>
+          <t>-67,8; -49,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,96; 59,01</t>
+          <t>31,44; 57,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 14,0</t>
+          <t>-8,49; 12,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-64,88; -50,78</t>
+          <t>-63,9; -51,14</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,09; 21,86</t>
+          <t>13,31; 22,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 7,73</t>
+          <t>-1,05; 7,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,29; -13,86</t>
+          <t>-25,19; -13,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,43; 24,73</t>
+          <t>15,97; 25,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 13,06</t>
+          <t>3,78; 12,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,12; -8,42</t>
+          <t>-16,16; -8,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,73; 22,16</t>
+          <t>15,96; 22,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 8,92</t>
+          <t>2,81; 9,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-21,55; -12,48</t>
+          <t>-21,68; -12,59</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,15; 77,33</t>
+          <t>40,13; 77,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 27,32</t>
+          <t>-3,52; 26,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-79,88; -46,22</t>
+          <t>-80,37; -46,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,0; 75,95</t>
+          <t>42,9; 78,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,17; 39,74</t>
+          <t>10,08; 39,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,64; -25,84</t>
+          <t>-42,99; -25,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,59; 71,2</t>
+          <t>46,0; 71,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 28,69</t>
+          <t>8,15; 29,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,24; -39,6</t>
+          <t>-65,27; -40,07</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,93; 21,53</t>
+          <t>10,78; 21,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 7,39</t>
+          <t>-2,41; 7,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,59; -12,83</t>
+          <t>-21,64; -12,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,25; 24,92</t>
+          <t>13,74; 25,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 11,27</t>
+          <t>1,52; 11,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 29,03</t>
+          <t>-18,86; 34,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,37; 21,49</t>
+          <t>14,25; 21,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 7,96</t>
+          <t>1,05; 8,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 18,91</t>
+          <t>-18,39; 17,59</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,7; 83,27</t>
+          <t>34,76; 83,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 28,08</t>
+          <t>-7,92; 29,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,59; -47,0</t>
+          <t>-69,67; -47,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39,48; 81,46</t>
+          <t>37,01; 82,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,96; 36,78</t>
+          <t>4,17; 36,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,41; 89,64</t>
+          <t>-55,27; 109,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,13; 74,08</t>
+          <t>43,2; 75,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,75; 27,4</t>
+          <t>3,18; 28,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-57,57; 63,41</t>
+          <t>-58,15; 59,71</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,58; 17,19</t>
+          <t>7,8; 16,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 4,42</t>
+          <t>-3,86; 4,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,81; -11,73</t>
+          <t>-19,48; -12,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,82; 18,27</t>
+          <t>9,55; 17,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 6,28</t>
+          <t>-2,48; 5,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-23,73; -16,57</t>
+          <t>-24,2; -16,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,99; 16,07</t>
+          <t>10,06; 16,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 3,97</t>
+          <t>-1,98; 3,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-20,4; -15,19</t>
+          <t>-20,36; -15,29</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>29,87; 70,38</t>
+          <t>26,95; 67,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 18,32</t>
+          <t>-13,59; 17,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-66,62; -47,72</t>
+          <t>-66,61; -47,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27,96; 60,75</t>
+          <t>27,52; 58,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 20,48</t>
+          <t>-7,19; 18,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-69,54; -54,15</t>
+          <t>-70,55; -54,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,9; 56,28</t>
+          <t>32,09; 56,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 13,96</t>
+          <t>-6,3; 13,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-65,08; -53,54</t>
+          <t>-65,57; -53,45</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13,19; 17,96</t>
+          <t>13,2; 17,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 4,29</t>
+          <t>-0,05; 4,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,26; -15,32</t>
+          <t>-19,94; -14,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,81; 19,48</t>
+          <t>14,8; 19,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,01; 6,67</t>
+          <t>1,87; 6,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 2,2</t>
+          <t>-18,47; 1,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,47; 18,06</t>
+          <t>14,74; 18,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,92</t>
+          <t>1,56; 4,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-18,13; -6,23</t>
+          <t>-18,07; -8,1</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>42,97; 63,68</t>
+          <t>43,88; 64,65</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 15,29</t>
+          <t>-0,09; 16,13</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-67,55; -53,93</t>
+          <t>-67,86; -53,66</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40,97; 58,15</t>
+          <t>41,2; 57,95</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,62; 20,09</t>
+          <t>5,14; 20,41</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-52,56; 6,55</t>
+          <t>-52,76; 4,24</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,71; 58,58</t>
+          <t>44,76; 58,34</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>4,83; 15,87</t>
+          <t>4,8; 15,76</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-56,45; -19,62</t>
+          <t>-56,4; -25,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R2-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-17,8</t>
+          <t>-17,79</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-21,99</t>
+          <t>-20,83</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-19,79</t>
+          <t>-19,23</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,03; 21,23</t>
+          <t>10,59; 21,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 8,49</t>
+          <t>-2,12; 7,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,11; -13,38</t>
+          <t>-22,22; -13,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 19,2</t>
+          <t>8,75; 19,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 3,68</t>
+          <t>-6,18; 4,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,78; -17,49</t>
+          <t>-25,29; -16,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,27; 18,86</t>
+          <t>11,52; 19,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 4,23</t>
+          <t>-2,75; 4,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-23,03; -16,84</t>
+          <t>-22,0; -15,78</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-57,66%</t>
+          <t>-57,63%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-57,87%</t>
+          <t>-54,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-57,48%</t>
+          <t>-55,87%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,58; 76,02</t>
+          <t>31,74; 75,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 29,77</t>
+          <t>-6,55; 27,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-66,12; -45,55</t>
+          <t>-66,98; -47,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,26; 55,19</t>
+          <t>20,77; 53,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,37; 10,46</t>
+          <t>-15,07; 11,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,8; -49,59</t>
+          <t>-62,45; -47,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,44; 57,84</t>
+          <t>31,51; 58,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 12,95</t>
+          <t>-7,58; 14,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-63,9; -51,14</t>
+          <t>-61,36; -48,6</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-18,52</t>
+          <t>-13,94</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-12,17</t>
+          <t>-12,07</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-15,93</t>
+          <t>-12,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,31; 22,09</t>
+          <t>12,92; 21,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 7,54</t>
+          <t>-0,9; 7,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,19; -13,84</t>
+          <t>-18,12; -9,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,97; 25,38</t>
+          <t>15,8; 25,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 12,96</t>
+          <t>3,84; 12,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,16; -8,26</t>
+          <t>-15,82; -8,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,96; 22,24</t>
+          <t>16,44; 22,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 9,04</t>
+          <t>2,79; 8,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-21,68; -12,59</t>
+          <t>-15,67; -10,21</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-60,38%</t>
+          <t>-45,46%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-34,96%</t>
+          <t>-34,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-48,62%</t>
+          <t>-39,63%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,13; 77,53</t>
+          <t>39,74; 76,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 26,4</t>
+          <t>-2,61; 26,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-80,37; -46,89</t>
+          <t>-54,97; -34,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42,9; 78,66</t>
+          <t>42,29; 76,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,08; 39,83</t>
+          <t>10,75; 40,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,99; -25,38</t>
+          <t>-42,62; -26,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,0; 71,86</t>
+          <t>47,67; 74,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,15; 29,19</t>
+          <t>8,28; 28,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,27; -40,07</t>
+          <t>-45,84; -32,71</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-17,21</t>
+          <t>-16,93</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>-15,99</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-6,55</t>
+          <t>-16,45</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,78; 21,03</t>
+          <t>11,29; 21,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 7,63</t>
+          <t>-2,38; 7,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,64; -12,58</t>
+          <t>-21,24; -12,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,74; 25,05</t>
+          <t>14,49; 24,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 11,22</t>
+          <t>1,18; 11,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 34,18</t>
+          <t>-20,11; -11,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,25; 21,93</t>
+          <t>14,58; 21,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 8,31</t>
+          <t>0,46; 7,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 17,59</t>
+          <t>-19,6; -13,65</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-60,33%</t>
+          <t>-59,37%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>-47,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-21,11%</t>
+          <t>-53,03%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,76; 83,16</t>
+          <t>35,56; 82,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 29,37</t>
+          <t>-7,69; 30,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,67; -47,95</t>
+          <t>-68,75; -47,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37,01; 82,23</t>
+          <t>39,33; 80,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,17; 36,59</t>
+          <t>3,16; 35,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,27; 109,2</t>
+          <t>-55,89; -36,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,2; 75,49</t>
+          <t>43,74; 73,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,18; 28,57</t>
+          <t>1,48; 27,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-58,15; 59,71</t>
+          <t>-59,84; -45,98</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-15,46</t>
+          <t>-14,69</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-19,96</t>
+          <t>-18,2</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-17,8</t>
+          <t>-16,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,8; 16,77</t>
+          <t>8,17; 16,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 4,43</t>
+          <t>-3,65; 4,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,48; -12,23</t>
+          <t>-18,35; -11,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,55; 17,69</t>
+          <t>9,08; 17,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 5,79</t>
+          <t>-2,3; 6,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,2; -16,61</t>
+          <t>-21,51; -14,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,06; 16,14</t>
+          <t>9,91; 16,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 3,88</t>
+          <t>-2,3; 3,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-20,36; -15,29</t>
+          <t>-19,12; -14,14</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-57,67%</t>
+          <t>-54,8%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-61,15%</t>
+          <t>-55,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-59,59%</t>
+          <t>-55,31%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>26,95; 67,43</t>
+          <t>28,01; 67,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 17,66</t>
+          <t>-12,62; 17,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-66,61; -47,81</t>
+          <t>-62,95; -44,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27,52; 58,32</t>
+          <t>26,23; 58,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 18,57</t>
+          <t>-6,56; 21,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-70,55; -54,45</t>
+          <t>-62,03; -48,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,09; 56,83</t>
+          <t>30,93; 56,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 13,75</t>
+          <t>-7,25; 13,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-65,57; -53,45</t>
+          <t>-60,56; -49,58</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-17,22</t>
+          <t>-15,6</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-13,16</t>
+          <t>-16,5</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-15,07</t>
+          <t>-16,03</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13,2; 17,91</t>
+          <t>13,37; 17,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 4,53</t>
+          <t>-0,15; 4,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,94; -14,99</t>
+          <t>-17,47; -13,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,8; 19,41</t>
+          <t>14,45; 19,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,83</t>
+          <t>1,73; 6,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 1,43</t>
+          <t>-18,44; -14,41</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,74; 18,19</t>
+          <t>14,77; 18,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,89</t>
+          <t>1,38; 4,67</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-18,07; -8,1</t>
+          <t>-17,53; -14,72</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-59,07%</t>
+          <t>-53,51%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-38,12%</t>
+          <t>-47,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-47,26%</t>
+          <t>-50,28%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>43,88; 64,65</t>
+          <t>44,03; 63,77</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 16,13</t>
+          <t>-0,46; 16,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-67,86; -53,66</t>
+          <t>-58,05; -48,38</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41,2; 57,95</t>
+          <t>40,18; 57,83</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,14; 20,41</t>
+          <t>4,78; 19,03</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-52,76; 4,24</t>
+          <t>-51,72; -42,9</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,76; 58,34</t>
+          <t>45,14; 58,5</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>4,8; 15,76</t>
+          <t>3,98; 14,9</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-56,4; -25,65</t>
+          <t>-53,51; -47,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R2-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son no remunerados</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
